--- a/기능정의서/FO/06_계정_회원가입·로그인·내정보_기능정의서.xlsx
+++ b/기능정의서/FO/06_계정_회원가입·로그인·내정보_기능정의서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhcho/Documents/Myanmar/기능정의서/FO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C71711-CC73-8841-8E06-0BC4988C46EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E99CD66-352E-3244-B092-99500139EC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -529,18 +529,6 @@
   </si>
   <si>
     <t>**1. 섹션 개요**
-- STEP1: 기본 정보 + 증명사진.
-**2. 입력 항목**
-- 한글/영문 성명 · 생년월일 · 성별 · 국적 · 제1언어 · 연락처 · 직업(코드) · 응시동기(코드) · 응시목적(코드) · 여권번호.
-- 증명사진(jpg/png, 3:4 비율, 200KB~2MB) — 미리보기.
-**3. 검증**
-- 모든 필수 항목, 사진 규격 1차 검증(파일형식/크기/비율).
-**4. 비고**
-- 직업·응시동기·응시목적 코드는 ‘연명부 양식’ 코드와 일치(직업 1~12 / 응시동기 1~11 / 응시목적 1~15).</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>**1. 섹션 개요**
 - STEP2: 이메일·비밀번호 설정.
 **2. 검증**
 - 이메일 형식 검증, 중복 가입 확인.
@@ -560,6 +548,18 @@
 - 새 사진 등록 시 BO 사진 심사 재실행 — 다음 회차부터 반영(현재 진행 중인 접수 건은 영향 없음).
 **5. 비고**
 - 고객사 수정(0519) — 시험 접수 시 회원정보 readonly 처리의 기반.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>**1. 섹션 개요**
+- STEP1: 기본 정보 + 증명사진.
+**2. 입력 항목**
+- 한글/영문 성명 · 생년월일 · 성별 · 국적 · 제1언어 · 연락처 · 직업(코드) · 응시동기(코드) · 응시목적(코드)
+- 증명사진(jpg/png, 3:4 비율, 200KB~2MB) — 미리보기.
+**3. 검증**
+- 모든 필수 항목, 사진 규격 1차 검증(파일형식/크기/비율).
+**4. 비고**
+- 직업·응시동기·응시목적 코드는 ‘연명부 양식’ 코드와 일치(직업 1~12 / 응시동기 1~11 / 응시목적 1~15).</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -756,12 +756,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -774,6 +768,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,22 +1099,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="18">
       <c r="A2" s="11" t="s">
@@ -1399,7 +1399,7 @@
         <v>23</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>52</v>
@@ -1441,7 +1441,7 @@
         <v>23</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M9" s="12" t="s">
         <v>57</v>
@@ -1565,7 +1565,7 @@
         <v>75</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>76</v>
@@ -1601,79 +1601,79 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="18">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="17"/>
     </row>
     <row r="15" spans="1:2" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
@@ -1780,23 +1780,23 @@
       </c>
     </row>
     <row r="33" spans="1:2" ht="18">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="16" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" customHeight="1">
-      <c r="A35" s="16"/>
-      <c r="B35" s="17"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
     </row>
     <row r="36" spans="1:2" ht="18" customHeight="1">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17" t="s">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15" t="s">
         <v>108</v>
       </c>
     </row>
